--- a/ros2_ws/src/flychams_bringup/config/Configuration-Test.xlsx
+++ b/ros2_ws/src/flychams_bringup/config/Configuration-Test.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="320">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -953,9 +953,6 @@
   </si>
   <si>
     <t xml:space="preserve">Operational Conditions O1 (ultra-high-resolution camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7680x4320)</t>
   </si>
   <si>
     <t xml:space="preserve">CAM05</t>
@@ -2337,22 +2334,22 @@
         <v>2</v>
       </c>
       <c r="C2" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="D2" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="E2" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="G2" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="H2" s="20" t="s">
         <v>315</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>316</v>
       </c>
       <c r="I2" s="20" t="s">
         <v>290</v>
@@ -2371,28 +2368,28 @@
         <v>147</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0.4</v>
@@ -6013,7 +6010,7 @@
         <v>294</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>296</v>
@@ -6040,16 +6037,16 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>309</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>310</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>294</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>296</v>

--- a/ros2_ws/src/flychams_bringup/config/Configuration-Test.xlsx
+++ b/ros2_ws/src/flychams_bringup/config/Configuration-Test.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="333">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -64,6 +64,9 @@
     <t xml:space="preserve">StartHour</t>
   </si>
   <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
     <t xml:space="preserve">MISSION00</t>
   </si>
   <si>
@@ -94,9 +97,6 @@
     <t xml:space="preserve">(16:30:00)</t>
   </si>
   <si>
-    <t xml:space="preserve">X</t>
-  </si>
-  <si>
     <t xml:space="preserve">MISSION01</t>
   </si>
   <si>
@@ -463,6 +463,9 @@
     <t xml:space="preserve">RefFocal [mm]</t>
   </si>
   <si>
+    <t xml:space="preserve">StreamURL</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA00</t>
   </si>
   <si>
@@ -484,6 +487,9 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=90.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5000</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA01</t>
   </si>
   <si>
@@ -502,6 +508,9 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=0.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5001</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA02</t>
   </si>
   <si>
@@ -511,6 +520,9 @@
     <t xml:space="preserve">(X=0.0, Y=0.3, Z=-0.15)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5002</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA03</t>
   </si>
   <si>
@@ -523,6 +535,9 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=180.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5003</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA04</t>
   </si>
   <si>
@@ -535,6 +550,9 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=270.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5004</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA05</t>
   </si>
   <si>
@@ -598,24 +616,36 @@
     <t xml:space="preserve">Tracking Head 2 Multi-Camera 2 (Multi)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5005</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA15</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head Multi-Camera 3 (Multi)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5006</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA16</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 Multi-Camera 3 (Multi)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5007</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA17</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 Multi-Camera 3 (Multi)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5008</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA18</t>
   </si>
   <si>
@@ -676,16 +706,25 @@
     <t xml:space="preserve">Central Head Multi-Hybrid 3 (Multi)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5009</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA28</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 Multi-Hybrid 3 (Multi)</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:5010</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA29</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 Multi-Hybrid 3 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">udp://127.0.0.1:5011</t>
   </si>
   <si>
     <t xml:space="preserve">Resolution [pix]</t>
@@ -1000,7 +1039,7 @@
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1061,6 +1100,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1161,7 +1207,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1194,7 +1240,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1206,12 +1252,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1795,36 +1845,38 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="B3" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
@@ -1873,9 +1925,7 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>21</v>
-      </c>
+      <c r="A4" s="13"/>
       <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
@@ -1883,28 +1933,28 @@
         <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -1953,7 +2003,7 @@
       <c r="BD4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="9" t="s">
         <v>25</v>
       </c>
@@ -1961,28 +2011,28 @@
         <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
@@ -2031,7 +2081,7 @@
       <c r="BD5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
@@ -2039,7 +2089,7 @@
         <v>29</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>30</v>
@@ -2048,19 +2098,19 @@
         <v>31</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
@@ -2109,7 +2159,7 @@
       <c r="BD6" s="12"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="9" t="s">
         <v>32</v>
       </c>
@@ -2117,7 +2167,7 @@
         <v>33</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>30</v>
@@ -2126,19 +2176,19 @@
         <v>34</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
@@ -2187,7 +2237,7 @@
       <c r="BD7" s="12"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="9" t="s">
         <v>35</v>
       </c>
@@ -2195,7 +2245,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>30</v>
@@ -2204,19 +2254,19 @@
         <v>37</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
@@ -2312,92 +2362,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>315</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>292</v>
+      <c r="C2" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>305</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="C3" s="21" t="b">
+      <c r="A3" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="E3" s="21" t="b">
+      <c r="D3" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="E3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="G3" s="21" t="b">
+      <c r="F3" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>319</v>
-      </c>
-      <c r="I3" s="21" t="n">
+      <c r="H3" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="I3" s="22" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="22" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2450,12 +2500,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -2477,7 +2527,7 @@
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>40</v>
@@ -2485,7 +2535,7 @@
       <c r="C3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2499,7 +2549,7 @@
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2539,15 +2589,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -2643,7 +2693,7 @@
       <c r="D3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -2724,7 +2774,7 @@
       <c r="D4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="16" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -2800,12 +2850,12 @@
         <v>61</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="16" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -2886,7 +2936,7 @@
       <c r="D6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="16" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="9" t="s">
@@ -2999,50 +3049,50 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
       <c r="XFC1" s="3"/>
       <c r="XFD1" s="3"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="18" t="s">
         <v>73</v>
       </c>
       <c r="L2" s="12"/>
@@ -3057,390 +3107,390 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="C3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>12000</v>
       </c>
       <c r="XFC3" s="3"/>
       <c r="XFD3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="19" t="n">
         <v>12000</v>
       </c>
       <c r="XFC5" s="3"/>
       <c r="XFD5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="18" t="n">
+      <c r="J14" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -3489,32 +3539,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>112</v>
       </c>
       <c r="H2" s="12"/>
@@ -3530,22 +3580,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3555,22 +3605,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3580,22 +3630,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3610,22 +3660,22 @@
       <c r="XFD5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3635,22 +3685,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3660,22 +3710,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -3685,22 +3735,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -3710,22 +3760,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -3735,22 +3785,22 @@
       <c r="XEY10" s="3"/>
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" s="2"/>
@@ -3760,22 +3810,22 @@
       <c r="XEY11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G12" s="2"/>
@@ -3785,22 +3835,22 @@
       <c r="XEY12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G13" s="2"/>
@@ -3810,22 +3860,22 @@
       <c r="XEY13" s="3"/>
     </row>
     <row r="14" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G14" s="2"/>
@@ -3874,1149 +3924,1212 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="36.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="2" width="27.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="12" style="12" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="2" width="27.34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="13" style="12" width="11"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="15" style="2" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="3" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="2"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="18" t="s">
         <v>143</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="B3" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="H3" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="18" t="n">
+      <c r="K3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="2"/>
+      <c r="L3" s="19" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H5" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="I5" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" s="18" t="s">
+      <c r="XFD8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" s="18" t="s">
+      <c r="E12" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="E13" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="G13" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I13" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J13" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="K13" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="L13" s="19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G16" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="H16" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E5" s="18" t="s">
+      <c r="I16" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G5" s="18" t="s">
+      <c r="E18" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="XFD21" s="3"/>
+    </row>
+    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="XFD22" s="3"/>
+    </row>
+    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="H23" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="XFD23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I25" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J25" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="18" t="n">
+      <c r="K25" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G6" s="18" t="s">
+      <c r="L25" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="H6" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="I6" s="18" t="n">
+      <c r="H26" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I26" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J26" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K6" s="18" t="n">
+      <c r="K26" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="I7" s="18" t="n">
+      <c r="L26" s="19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I28" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J28" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K7" s="18" t="n">
+      <c r="K28" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F8" s="18" t="s">
+      <c r="L28" s="19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E29" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="F29" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F30" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="G30" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="H30" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I30" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J30" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="18" t="n">
+      <c r="K30" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="XFD8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F9" s="18" t="s">
+      <c r="L30" s="19" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E31" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="G9" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G10" s="18" t="s">
+      <c r="F31" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="E32" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F32" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="G32" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I32" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J32" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K10" s="18" t="n">
+      <c r="K32" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K19" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" s="2"/>
-      <c r="XFD21" s="3"/>
-    </row>
-    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="2"/>
-      <c r="XFD22" s="3"/>
-    </row>
-    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="2"/>
-      <c r="XFD23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K25" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I26" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K26" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K28" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I29" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="H31" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="I31" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K31" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I32" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="2"/>
+      <c r="L32" s="19" t="s">
+        <v>231</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5054,37 +5167,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>222</v>
+      <c r="D2" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>235</v>
       </c>
       <c r="XEV2" s="3"/>
       <c r="XEW2" s="3"/>
@@ -5097,416 +5210,416 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="C3" s="18" t="s">
+      <c r="A3" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E3" s="18" t="n">
+      <c r="D3" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="A4" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E4" s="18" t="n">
+      <c r="D4" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="C5" s="18" t="s">
+      <c r="A5" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E5" s="18" t="n">
+      <c r="D5" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C6" s="18" t="s">
+      <c r="A6" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E6" s="18" t="n">
+      <c r="D6" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C7" s="18" t="s">
+      <c r="A7" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E7" s="18" t="n">
+      <c r="D7" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="C8" s="18" t="s">
+      <c r="A8" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" s="18" t="n">
+      <c r="D8" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="C9" s="18" t="s">
+      <c r="A9" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E9" s="18" t="n">
+      <c r="D9" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E9" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="C11" s="18" t="s">
+      <c r="A11" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E11" s="18" t="n">
+      <c r="D11" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E11" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="C12" s="18" t="s">
+      <c r="A12" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D12" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E12" s="18" t="n">
+      <c r="D12" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="C13" s="18" t="s">
+      <c r="A13" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E13" s="18" t="n">
+      <c r="D13" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E13" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="C14" s="18" t="s">
+      <c r="A14" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E14" s="18" t="n">
+      <c r="D14" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="C15" s="18" t="s">
+      <c r="A15" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E15" s="18" t="n">
+      <c r="D15" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="C16" s="18" t="s">
+      <c r="A16" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="18" t="n">
+      <c r="D16" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="C17" s="18" t="s">
+      <c r="A17" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E17" s="18" t="n">
+      <c r="D17" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C18" s="18" t="s">
+      <c r="A18" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E18" s="18" t="n">
+      <c r="D18" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="C19" s="18" t="s">
+      <c r="A19" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E19" s="18" t="n">
+      <c r="D19" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E19" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="C20" s="18" t="s">
+      <c r="A20" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D20" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E20" s="18" t="n">
+      <c r="D20" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
@@ -5551,200 +5664,200 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="P2" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="F2" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="L2" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q2" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="R2" s="21" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="D3" s="21" t="n">
+      <c r="C3" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="21" t="n">
+      <c r="E3" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="21" t="b">
+      <c r="F3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="H3" s="21" t="b">
+      <c r="G3" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="H3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="J3" s="21" t="b">
+      <c r="I3" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="J3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="L3" s="21" t="b">
+      <c r="K3" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="L3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="N3" s="21" t="n">
+      <c r="M3" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="N3" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="21" t="n">
+      <c r="O3" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="21" t="n">
+      <c r="P3" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="21" t="n">
+      <c r="Q3" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="21" t="n">
+      <c r="R3" s="22" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="D4" s="21" t="n">
+      <c r="C4" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="D4" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="21" t="b">
+      <c r="F4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="H4" s="21" t="b">
+      <c r="G4" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="H4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I4" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="J4" s="21" t="b">
+      <c r="I4" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="J4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K4" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="L4" s="21" t="b">
+      <c r="K4" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="L4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M4" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="N4" s="21" t="n">
+      <c r="M4" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="N4" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O4" s="21" t="n">
+      <c r="O4" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" s="21" t="n">
+      <c r="P4" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q4" s="21" t="n">
+      <c r="Q4" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R4" s="21" t="n">
+      <c r="R4" s="22" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5803,271 +5916,271 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>292</v>
+      <c r="D2" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>305</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="G3" s="21" t="b">
+      <c r="A3" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="I3" s="21" t="n">
+      <c r="H3" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="I3" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="G4" s="21" t="b">
+      <c r="A4" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="I4" s="21" t="n">
+      <c r="H4" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="I4" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G5" s="21" t="b">
+      <c r="A5" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="G5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="I5" s="21" t="n">
+      <c r="H5" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="I5" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G6" s="21" t="b">
+      <c r="A6" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="G6" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H6" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="I6" s="21" t="n">
+      <c r="H6" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="I6" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="C7" s="22" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="G7" s="21" t="b">
+      <c r="D7" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="G7" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H7" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="I7" s="21" t="n">
+      <c r="H7" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="I7" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="K7" s="22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>308</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="E8" s="22" t="s">
         <v>309</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G8" s="21" t="b">
+      <c r="F8" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="G8" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="I8" s="21" t="n">
+      <c r="H8" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="I8" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="K8" s="22" t="n">
         <v>6</v>
       </c>
     </row>
